--- a/raw-xlsx/183Jagatballavpur_2026_Form20.xlsx
+++ b/raw-xlsx/183Jagatballavpur_2026_Form20.xlsx
@@ -12334,7 +12334,7 @@
       </c>
       <c r="L282" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Maju</t>
+          <t>Maju</t>
         </is>
       </c>
     </row>
